--- a/data/credit_bond_all_2026-08-24.xlsx
+++ b/data/credit_bond_all_2026-08-24.xlsx
@@ -2064,59 +2064,59 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26安租Y6</t>
+          <t>26中铁十一MTN002B</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>08-24 19:00</t>
+          <t>08-24 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>245894.SH</t>
+          <t>102683318.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.5</v>
+        <v>7.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>88.72</v>
+        <v>73.49</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26安租Y4</t>
+          <t>26中铁十一MTN001B</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.64Y+N</t>
+          <t>4.97Y+N</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.9643</t>
+          <t>2.1286</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司</t>
+          <t>中铁十一局集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 19.33</t>
+          <t>C+ 30.79</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2151,21 +2151,23 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V9" s="3"/>
+        <v>2.1</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2173,45 +2175,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司到期或回售的公司债券本金或置换偿还公司债券本金的自有资金[21安租08,24安租Y2,22安租17]</t>
+          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为7亿元,发行人拟将募集资金用于偿还发行人本部及子公司有息债务本息。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,中信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)(品种二)</t>
+          <t>中铁十一局集团有限公司2026年度第二期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2221,64 +2219,60 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>市政路桥</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2299,64 +2293,60 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26中铁十一MTN002B</t>
+          <t>26安租Y5(取消发行)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>08-24 18:00</t>
+          <t>08-24 19:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683318.IB</t>
+          <t>DY245893.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>73.49</v>
-      </c>
+          <t>1.70 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26中铁十一MTN001B</t>
+          <t>26安租Y4</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.97Y+N</t>
+          <t>1.64Y+N</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2.1286</t>
+          <t>1.9643</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2366,12 +2356,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司</t>
+          <t>平安国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.79</t>
+          <t>C- 19.33</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2391,23 +2381,19 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>1.25</v>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2415,41 +2401,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z10" s="3"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为7亿元,发行人拟将募集资金用于偿还发行人本部及子公司有息债务本息。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司到期或回售的公司债券本金或置换偿还公司债券本金的自有资金[21安租08,24安租Y2,22安租17]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>平安证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司2026年度第二期中期票据(品种二)</t>
+          <t>平安国际融资租赁有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2459,53 +2449,57 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2028-08-26</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2520,7 +2514,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2533,14 +2527,12 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26安租Y5(取消发行)</t>
+          <t>26渝旅03</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2550,118 +2542,126 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>DY245893.SH</t>
+          <t>283778.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>93.49</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>26渝旅01</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>4.89Y</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>2.2744</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>--/2.2000</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>重庆文化旅游集团有限公司</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.37</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>08-24 16:00</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>26安租Y4</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>1.64Y+N</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>1.9643</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>平安国际融资租赁有限公司</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>C- 19.33</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>08-24 15:00</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>2.66</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>2.42%~2.52%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司到期或回售的公司债券本金或置换偿还公司债券本金的自有资金[21安租08,24安租Y2,22安租17]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券或置换到期公司债券本金[23渝旅02]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>中信证券股份有限公司,西南证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>华中(武汉)融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2679,24 +2679,20 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)(品种一)(取消发行)</t>
+          <t>重庆文化旅游集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2714,32 +2710,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2749,17 +2745,17 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY11" s="3" t="inlineStr">
@@ -2772,74 +2768,74 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26渝旅03</t>
+          <t>26中建五局SCP003</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>08-24 19:00</t>
+          <t>08-24 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>283778.SH</t>
+          <t>012682139.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.5</v>
+        <v>10.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.32</v>
+        <v>1.39</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>93.49</v>
+        <v>20.55</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26渝旅01</t>
+          <t>26中建五局MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>4.89Y</t>
+          <t>2.59Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.2744</t>
+          <t>1.6824</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/2.2000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>重庆文化旅游集团有限公司</t>
+          <t>中国建筑第五工程局有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.37</t>
+          <t>B- 39.65</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2849,7 +2845,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>08-24 16:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2859,133 +2855,135 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V12" s="3"/>
+        <v>1.2</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.42%~2.52%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券或置换到期公司债券本金[23渝旅02]</t>
+          <t>发行人本期发行的10亿元超短期融资券募集资金扣除发行费用后,拟用于偿还发行人本部的银行贷款本金。</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,西南证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>华中(武汉)融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,渤海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>重庆文化旅游集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
+          <t>中国建筑第五工程局有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AK12" s="3"/>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>其他房建</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>旅游综合</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -3008,7 +3006,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26中建五局SCP003</t>
+          <t>26广核国际MTN002</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3018,12 +3016,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>012682139.IB</t>
+          <t>102683322.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -3034,48 +3032,48 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.65 ~ 2.05</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20.55</v>
+        <v>36.49</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26中建五局MTN001</t>
+          <t>23广核国际MTN001</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.59Y</t>
+          <t>2.25Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6824</t>
+          <t>1.7218</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第五工程局有限公司</t>
+          <t>中广核国际有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 39.65</t>
+          <t>B- 45.38</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3099,19 +3097,19 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="V13" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3122,23 +3120,27 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>香港特别行政区-新界</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行的10亿元超短期融资券募集资金扣除发行费用后,拟用于偿还发行人本部的银行贷款本金。</t>
+          <t>本期中期票据发行金额为人民币10亿元,募集资金将归集至发行人开立的NRA账户。实际募集资金扣除承销费后拟用于偿还发行人境外到期金融机构借款</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD13" s="3"/>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>中国广核集团有限公司</t>
+        </is>
+      </c>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3153,7 +3155,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第五工程局有限公司2026年度第三期超短期融资券</t>
+          <t>中广核国际有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3163,14 +3165,10 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3193,27 +3191,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3223,7 +3221,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW13" s="3" t="inlineStr">
@@ -3246,7 +3244,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26广核国际MTN002</t>
+          <t>26夏商MTN001</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3256,64 +3254,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683322.IB</t>
+          <t>102683307.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.05</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>36.49</v>
+        <v>44.72</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>23广核国际MTN001</t>
+          <t>25夏商MTN001(乡村振兴)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.25Y</t>
+          <t>325D+N</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7218</t>
+          <t>1.6583</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>中广核国际有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 45.38</t>
+          <t>C 27.86</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3337,47 +3335,43 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.18</v>
+        <v>3.06</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.0</v>
+        <v>1.2</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>香港特别行政区-新界</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元,募集资金将归集至发行人开立的NRA账户。实际募集资金扣除承销费后拟用于偿还发行人境外到期金融机构借款</t>
+          <t>本次发行5亿元中期票据，拟用于偿还发行人本部债务融资工具[26夏商SCP017]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>中国广核集团有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -3385,7 +3379,7 @@
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
@@ -3395,7 +3389,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>中广核国际有限公司2026年度第二期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3405,10 +3399,14 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2029-08-25</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3431,27 +3429,27 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3461,12 +3459,12 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3479,12 +3477,14 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26夏商MTN001</t>
+          <t>26广核电力MTN005</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3494,19 +3494,19 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683307.IB</t>
+          <t>102683314.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>1.7</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>44.72</v>
+        <v>31.49</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -3526,32 +3526,32 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25夏商MTN001(乡村振兴)</t>
+          <t>26广核电力MTN002</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>325D+N</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6583</t>
+          <t>1.6458</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>中国广核电力股份有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 27.86</t>
+          <t>B- 35.30</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3575,40 +3575,40 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.2</v>
+        <v>1.0</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次发行5亿元中期票据，拟用于偿还发行人本部债务融资工具[26夏商SCP017]</t>
+          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司贷款本息。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,渤海银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第一期中期票据</t>
+          <t>中国广核电力股份有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3639,14 +3639,10 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-08-25</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -3669,27 +3665,27 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3704,7 +3700,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3717,14 +3713,12 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN005</t>
+          <t>26国能江苏MTN003</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3734,7 +3728,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683314.IB</t>
+          <t>102683327.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3743,55 +3737,55 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>31.49</v>
+        <v>29.49</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN002</t>
+          <t>26国能江苏MTN002</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>2.85Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6742</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司</t>
+          <t>国家能源集团江苏电力有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 35.30</t>
+          <t>C 26.02</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3815,19 +3809,19 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3838,17 +3832,17 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司贷款本息。</t>
+          <t>本次中期票据注册总额度为20亿元,本期发行3亿元,期限5年,全部用于偿还公司本部及子公司有息债务以及补充营运资金。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3869,7 +3863,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司2026年度第五期中期票据</t>
+          <t>国家能源集团江苏电力有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3905,7 +3899,7 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3920,7 +3914,7 @@
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
@@ -3953,12 +3947,14 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26国能江苏MTN003</t>
+          <t>26宁河西MTN002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3968,64 +3964,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683327.IB</t>
+          <t>102683308.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>29.49</v>
+        <v>35.72</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26国能江苏MTN002</t>
+          <t>24宁河西MTN004B</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.85Y</t>
+          <t>3.15Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6742</t>
+          <t>1.7191</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团江苏电力有限公司</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 26.02</t>
+          <t>C- 24.17</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4049,10 +4045,10 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.6</v>
+        <v>4.3579</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4057,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4077,12 +4073,12 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册总额度为20亿元,本期发行3亿元,期限5年,全部用于偿还公司本部及子公司有息债务以及补充营运资金。</t>
+          <t>发行人本期发行19亿元中期票据将全部用于偿还发行人债务融资工具本金[21宁河西MTN003,23宁河西MTN002A]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,南京银行股份有限公司</t>
+          <t>南京银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4093,7 +4089,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4103,7 +4099,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团江苏电力有限公司2026年度第三期中期票据</t>
+          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4113,10 +4109,14 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2029-08-25</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4134,32 +4134,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4194,7 +4194,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26宁河西MTN002</t>
+          <t>26德阳经开MTN001B</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4204,64 +4204,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683308.IB</t>
+          <t>102683296.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>35.72</v>
+        <v>66.49</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>24宁河西MTN004B</t>
+          <t>25德阳经开MTN001</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>3.15Y</t>
+          <t>3.52Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7191</t>
+          <t>2.2598</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2500/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司</t>
+          <t>德阳经开区发展(控股)集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 24.17</t>
+          <t>D+ 5.10</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>08-24 09:00</t>
+          <t>08-24 10:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4285,43 +4285,51 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>4.3579</v>
+        <v>5.3</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>四川省-德阳市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行19亿元中期票据将全部用于偿还发行人债务融资工具本金[21宁河西MTN003,23宁河西MTN002A]</t>
+          <t>发行人本期中期票据发行金额为10.00亿元，拟使用募集资金10.00亿元偿还有息债务[21德阳经开MTN001]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3"/>
+          <t>长江证券股份有限公司,成都银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -4339,7 +4347,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>南京市河西新城区国有资产经营控股(集团)有限责任公司2026年度第二期中期票据</t>
+          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4349,14 +4357,10 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-08-25</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4364,7 +4368,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4374,12 +4378,12 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
@@ -4389,12 +4393,12 @@
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
@@ -4409,7 +4413,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
@@ -4427,14 +4431,12 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26德阳经开MTN001B</t>
+          <t>26广核国际MTN003</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4444,7 +4446,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683296.IB</t>
+          <t>102683323.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4453,55 +4455,55 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.65 ~ 2.05</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>66.49</v>
+        <v>36.49</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25德阳经开MTN001</t>
+          <t>23广核国际MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>3.52Y</t>
+          <t>2.25Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.2598</t>
+          <t>1.7218</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>2.2500/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>德阳经开区发展(控股)集团有限公司</t>
+          <t>中广核国际有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.10</t>
+          <t>B- 45.38</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4511,7 +4513,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>08-24 10:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4525,49 +4527,43 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.06</v>
-      </c>
+        <v>1.97</v>
+      </c>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>四川省-德阳市</t>
+          <t>香港特别行政区-新界</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10.00亿元，拟使用募集资金10.00亿元偿还有息债务[21德阳经开MTN001]</t>
+          <t>本期中期票据发行金额为人民币10亿元，募集资金将归集至发行人开立的NRA账户。实际募集资金扣除承销费后拟用于偿还发行人境外到期金融机构借款</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,成都银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
+          <t>中国广核集团有限公司</t>
         </is>
       </c>
       <c r="AE19" s="3" t="inlineStr">
@@ -4577,7 +4573,7 @@
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4587,7 +4583,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种二)</t>
+          <t>中广核国际有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4608,7 +4604,7 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
@@ -4618,32 +4614,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4676,7 +4672,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26广核国际MTN003</t>
+          <t>26甬交投集MTN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4686,12 +4682,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683323.IB</t>
+          <t>102683297.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -4702,14 +4698,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.05</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>36.49</v>
+        <v>52.72</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -4718,32 +4714,32 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>23广核国际MTN001</t>
+          <t>26甬交投集MTN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.25Y</t>
+          <t>2.44Y+N</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7218</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>1.7800/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>中广核国际有限公司</t>
+          <t>宁波交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 45.38</t>
+          <t>C+ 32.93</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4767,17 +4763,19 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V20" s="3"/>
+        <v>3.78</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>8.7</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4788,24 +4786,20 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>香港特别行政区-新界</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元，募集资金将归集至发行人开立的NRA账户。实际募集资金扣除承销费后拟用于偿还发行人境外到期金融机构借款</t>
+          <t>发行人本次中期票据拟发行10.00亿元,用途拟定为偿还发行人的有息负债</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国光大银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>中国广核集团有限公司</t>
-        </is>
-      </c>
+          <t>中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -4813,7 +4807,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4823,7 +4817,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>中广核国际有限公司2026年度第三期中期票据</t>
+          <t>宁波交通投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4833,10 +4827,14 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2029-08-25</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -4844,7 +4842,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4854,32 +4852,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4889,17 +4887,17 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY20" s="3" t="inlineStr">
@@ -4907,12 +4905,14 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26甬交投集MTN002</t>
+          <t>26上饶城投PPN003A(取消发行)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4922,64 +4922,58 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683297.IB</t>
+          <t>DY032680484.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>3.52</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>52.72</v>
-      </c>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26甬交投集MTN001</t>
+          <t>24上饶07</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.44Y+N</t>
+          <t>5.00Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>2.0440</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.7800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>宁波交通投资集团有限公司</t>
+          <t>上饶市城市建设投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.93</t>
+          <t>B- 41.86</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5002,47 +4996,43 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="U21" s="4" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>8.7</v>
-      </c>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江西省-上饶市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据拟发行10.00亿元,用途拟定为偿还发行人的有息负债</t>
+          <t>发行人本期定向债务融资工具注册规模为人民币6.79亿元,首期基础发行规模为人民币0亿元,发行规模上限为人民币6.52亿元,所募集资金拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5057,24 +5047,20 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>宁波交通投资集团有限公司2026年度第二期中期票据</t>
+          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-08-25</t>
-        </is>
-      </c>
-      <c r="AK21" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -5082,7 +5068,7 @@
       </c>
       <c r="AM21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AN21" s="3" t="inlineStr">
@@ -5092,32 +5078,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5132,12 +5118,12 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY21" s="3" t="inlineStr">
@@ -5152,7 +5138,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26上饶城投PPN003A(取消发行)</t>
+          <t>26上饶城投PPN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5162,43 +5148,49 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>DY032680484.IB</t>
+          <t>032680484.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>6.52</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>94.12</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24上饶07</t>
+          <t>24上饶08</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>5.00Y</t>
+          <t>5.05Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.0440</t>
+          <t>2.0540</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5236,7 +5228,9 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>3.1442</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
@@ -5245,7 +5239,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>2.42%~2.52%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5287,7 +5281,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具(品种一)(取消发行)</t>
+          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5297,7 +5291,7 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
+          <t>2033-08-25</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5378,7 +5372,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26上饶城投PPN003</t>
+          <t>26苏州资产MTN003</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5388,125 +5382,127 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>032680484.IB</t>
+          <t>102683315.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>1.45 ~ 1.75</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>25苏资K1</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>1.92Y</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>1.6565</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>--/1.6300</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>苏州资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>C 25.18</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>08-24 09:00</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>94.12</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>24上饶08</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>5.05Y</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>2.0540</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>上饶市城市建设投资开发集团有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>B- 41.86</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>08-24 09:00</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>3.1442</v>
-      </c>
-      <c r="V23" s="3"/>
+      <c r="V23" s="4" t="n">
+        <v>1.425</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2.42%~2.52%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江西省-上饶市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具注册规模为人民币6.79亿元,首期基础发行规模为人民币0亿元,发行规模上限为人民币6.52亿元,所募集资金拟用于偿还有息债务</t>
+          <t>本期债务融资工具发行拟募集资金规模5亿元,募集资金拟全部用于归还发行人存量债务融资工具本金[24苏州资产MTN002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
+          <t>南京银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5521,17 +5517,17 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>上饶市城市建设投资开发集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>苏州资产管理有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2033-08-25</t>
+          <t>2028-08-25</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5552,32 +5548,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5606,80 +5602,80 @@
         </is>
       </c>
       <c r="AZ23" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26苏州资产MTN003</t>
+          <t>26渝隆02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>08-24 18:00</t>
+          <t>08-24 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683315.IB</t>
+          <t>283771.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.75</t>
+          <t>1.80 ~ 2.30</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26.68</v>
+        <v>54.49</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25苏资K1</t>
+          <t>26渝隆01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>4.98Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6565</t>
+          <t>1.9474</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>1.9400/1.9300</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>苏州资产管理有限公司</t>
+          <t>重庆渝隆资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 25.18</t>
+          <t>C- 21.87</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5689,7 +5685,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>08-24 09:00</t>
+          <t>08-24 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5703,46 +5699,44 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>1.425</v>
-      </c>
+        <v>4.45</v>
+      </c>
+      <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>重庆市-九龙坡区</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金规模5亿元,募集资金拟全部用于归还发行人存量债务融资工具本金[24苏州资产MTN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后拟用于偿还回售的公司债券本金[23渝隆集团公司债02]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>西南证券股份有限公司,长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5752,28 +5746,28 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>苏州资产管理有限公司2026年度第三期中期票据</t>
+          <t>重庆渝隆资产经营(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2028-08-25</t>
+          <t>2031-08-25</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5788,32 +5782,32 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5841,14 +5835,12 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26渝隆02</t>
+          <t>26寿光01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5858,7 +5850,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283771.SH</t>
+          <t>520439.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5867,55 +5859,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.0</v>
+        <v>4.16</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.0</v>
+        <v>4.16</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.30</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>54.49</v>
+        <v>106.49</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26渝隆01</t>
+          <t>25寿光04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.98Y</t>
+          <t>3.96Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.9474</t>
+          <t>2.2840</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.9400/1.9300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>重庆渝隆资产经营(集团)有限公司</t>
+          <t>寿光市惠农新农村建设投资开发有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 21.87</t>
+          <t>B- 35.78</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5939,17 +5931,17 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.45</v>
+        <v>2.7404</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>2.30%~2.40%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5960,17 +5952,17 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>重庆市-九龙坡区</t>
+          <t>山东省-潍坊市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后拟用于偿还回售的公司债券本金[23渝隆集团公司债02]</t>
+          <t>本次公司债券募集资金扣除发行费用后,将用于偿还发行人到期的公司债券本金[24寿光01]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>西南证券股份有限公司,长城证券股份有限公司</t>
+          <t>财达证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5986,12 +5978,12 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>重庆渝隆资产经营(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>寿光市惠农新农村建设投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -6007,7 +5999,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -6022,32 +6014,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6080,74 +6072,74 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26寿光01</t>
+          <t>26郴投集团PPN004</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>08-24 19:00</t>
+          <t>08-24 18:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>520439.SZ</t>
+          <t>032680476.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.16</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.16</v>
+        <v>10.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>106.49</v>
+        <v>59.72</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>25寿光04</t>
+          <t>26郴发01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>3.96Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2.2840</t>
+          <t>1.8521</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>寿光市惠农新农村建设投资开发有限公司</t>
+          <t>郴州市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B- 35.78</t>
+          <t>C- 24.31</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6157,7 +6149,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>08-24 15:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6171,17 +6163,17 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.7404</v>
+        <v>4.85</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.30%~2.40%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6192,23 +6184,23 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>山东省-潍坊市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,将用于偿还发行人到期的公司债券本金[24寿光01]</t>
+          <t>本期定向债务融资工具发行规模为10亿元,拟全部用于偿还存量债务融资工具等有息债务的本金[23郴投集团MTN001]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>财达证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>交通银行股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6218,12 +6210,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>寿光市惠农新农村建设投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>郴州市发展投资集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6233,13 +6225,17 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2029-08-25</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
@@ -6259,22 +6255,22 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
@@ -6312,7 +6308,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26郴投集团PPN004</t>
+          <t>26埇桥城投PPN001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6322,64 +6318,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>032680476.IB</t>
+          <t>032680488.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
+        <v>0.6</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.0</v>
+        <v>0.6</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>59.72</v>
+        <v>60.68</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26郴发01</t>
+          <t>24埇桥城投PPN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>1.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8521</t>
+          <t>1.7601</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.9500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>郴州市发展投资集团有限公司</t>
+          <t>宿州埇桥城投集团(控股)有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 24.31</t>
+          <t>D- 1.43</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6403,41 +6399,51 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="V27" s="3"/>
+        <v>2.5167</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z27" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>安徽省-宿州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行规模为10亿元,拟全部用于偿还存量债务融资工具等有息债务的本金[23郴投集团MTN001]</t>
+          <t>发行人本期定向债务融资工具注册额度为6亿元,本期发行金额为0.60亿元,拟全部用于偿还公司有息债务。[21埇桥城投PPN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司,平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3"/>
+          <t>徽商银行股份有限公司,国信证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>安徽省信用融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE27" s="3" t="inlineStr">
         <is>
           <t>定向工具(PPN)</t>
@@ -6455,7 +6461,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>郴州市发展投资集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>宿州埇桥城投集团(控股)有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6465,14 +6471,10 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-08-25</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-08-25</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -6495,22 +6497,22 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6525,7 +6527,7 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
@@ -6548,7 +6550,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26埇桥城投PPN001</t>
+          <t>26浙资运营MTN002(科创债/并购)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6558,30 +6560,30 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>032680488.IB</t>
+          <t>102683326.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.6</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6</v>
+        <v>5.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>60.68</v>
+        <v>36.49</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -6590,17 +6592,17 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24埇桥城投PPN001</t>
+          <t>25浙资运营MTN002(科创债)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.24Y+2.00Y</t>
+          <t>3.72Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7601</t>
+          <t>1.7660</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6610,12 +6612,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>宿州埇桥城投集团(控股)有限公司</t>
+          <t>浙江省国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>D- 1.43</t>
+          <t>C- 21.93</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6639,54 +6641,46 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.5167</v>
+        <v>3.74</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.0</v>
+        <v>2.4</v>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>安徽省-宿州市</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具注册额度为6亿元,本期发行金额为0.60亿元,拟全部用于偿还公司有息债务。[21埇桥城投PPN001]</t>
+          <t>发行人本期科技创新债券(并购)拟募集资金5亿元,其中2.5亿元用于置换一年内通过基金出资等形式支持科技创新企业发展的自有资金,2.5亿元用于置换一年内购买控股子公司股份的自有出资部分。置换后的募集资金将用于偿还发行人有息债务等。</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,国信证券股份有限公司,申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3" t="inlineStr">
-        <is>
-          <t>安徽省信用融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,中国银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6701,17 +6695,17 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>宿州埇桥城投集团(控股)有限公司2026年度第一期定向债务融资工具</t>
+          <t>浙江省国有资本运营有限公司2026年度第二期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2028-08-25</t>
+          <t>2031-08-25</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6732,32 +6726,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6767,7 +6761,7 @@
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6790,7 +6784,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26浙资运营MTN002(科创债/并购)</t>
+          <t>26齐商银行永续债01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6800,49 +6794,49 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102683326.IB</t>
+          <t>242680030.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>36.49</v>
+        <v>126.49</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>25浙资运营MTN002(科创债)</t>
+          <t>24齐商银行永续债01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>3.72Y</t>
+          <t>2.82Y+N</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7660</t>
+          <t>2.5344</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6852,12 +6846,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>浙江省国有资本运营有限公司</t>
+          <t>齐商银行股份有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 21.93</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6877,50 +6871,50 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>2.4</v>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z29" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券(并购)拟募集资金5亿元,其中2.5亿元用于置换一年内通过基金出资等形式支持科技创新企业发展的自有资金,2.5亿元用于置换一年内购买控股子公司股份的自有出资部分。置换后的募集资金将用于偿还发行人有息债务等。</t>
+          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>其他金融债</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6935,7 +6929,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>浙江省国有资本运营有限公司2026年度第二期科技创新债券(并购)</t>
+          <t>齐商银行股份有限公司2026年无固定期限资本债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6945,53 +6939,53 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -7006,12 +7000,12 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AY29" s="3" t="inlineStr">
@@ -7024,74 +7018,74 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26甘肃农垦MTN002(乡村振兴)</t>
+          <t>26济南高新MTN007</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-24 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683329.IB</t>
+          <t>102683304.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>59.67</v>
+        <v>70.49</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26甘肃农垦MTN001(乡村振兴)</t>
+          <t>26济南高新MTN001B</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.45Y</t>
+          <t>4.44Y+N</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.8753</t>
+          <t>2.0834</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1100/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>甘肃省农垦集团有限责任公司</t>
+          <t>济南高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 29.17</t>
+          <t>C- 23.10</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7101,7 +7095,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>08-24 09:00</t>
+          <t>08-24 14:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7111,95 +7105,85 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>2.05%~2.15%</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>发行人本期中期票据发行规模5亿元,所募集的资金拟全部用于偿还发行人即将到期中期票据本金[23济南高新MTN004B]</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>济南高新控股集团有限公司2026年度第七期中期票据</t>
+        </is>
+      </c>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t>1.88%~1.98%</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA30" s="3" t="inlineStr">
-        <is>
-          <t>甘肃省-兰州市</t>
-        </is>
-      </c>
-      <c r="AB30" s="3" t="inlineStr">
-        <is>
-          <t>本期中期票据拟募集资金6亿元,其中:4.2亿元用于偿还发行人到期债务融资工具本金;1.8亿元用于乡村振兴领域。[23甘肃农垦MTN002(乡村振兴)]</t>
-        </is>
-      </c>
-      <c r="AC30" s="3" t="inlineStr">
-        <is>
-          <t>招商银行股份有限公司,中国农业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD30" s="3" t="inlineStr">
-        <is>
-          <t>甘肃省国有资产投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="AE30" s="3" t="inlineStr">
-        <is>
-          <t>中期票据</t>
-        </is>
-      </c>
-      <c r="AF30" s="3" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="AG30" s="3" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="AH30" s="3" t="inlineStr">
-        <is>
-          <t>甘肃省农垦集团有限责任公司2026年度第二期中期票据(乡村振兴)</t>
-        </is>
-      </c>
-      <c r="AI30" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AJ30" s="3" t="inlineStr">
-        <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
@@ -7207,7 +7191,7 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
@@ -7217,27 +7201,27 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>农业综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7247,12 +7231,12 @@
       </c>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7262,7 +7246,7 @@
       </c>
       <c r="AY30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AZ30" s="3"/>
@@ -7270,137 +7254,139 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26齐商银行永续债01</t>
+          <t>26深能Y3</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-24 18:00</t>
+          <t>08-24 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>242680030.IB</t>
+          <t>524972.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>126.49</v>
+        <v>49.72</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>24深能Y2</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>3.26Y+N</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>1.7712</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>1.7400/--</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>深圳能源集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>C 25.51</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>08-24 15:00</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>24齐商银行永续债01</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>2.82Y+N</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>2.5344</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>齐商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>C 27.50</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>08-24 09:00</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4" t="n">
+        <v>2.17</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还到期债务[23深能源MTN001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,国信证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>其他金融债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7410,12 +7396,12 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>齐商银行股份有限公司2026年无固定期限资本债券(第一期)</t>
+          <t>深圳能源集团股份有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7425,18 +7411,22 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t/>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7446,32 +7436,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7491,7 +7481,7 @@
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7504,74 +7494,74 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26济南高新MTN007</t>
+          <t>26龙源K1</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-24 18:00</t>
+          <t>08-24 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683304.IB</t>
+          <t>524981.SZ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>70.49</v>
+        <v>37.72</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26济南高新MTN001B</t>
+          <t>25龙源电力MTN001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.44Y+N</t>
+          <t>3.41Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.0834</t>
+          <t>1.7059</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>2.1100/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>济南高新控股集团有限公司</t>
+          <t>龙源电力集团股份有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 23.10</t>
+          <t>C- 24.41</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7581,7 +7571,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>08-24 14:00</t>
+          <t>08-24 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7591,21 +7581,21 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.52</v>
+        <v>5.78</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7613,45 +7603,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行规模5亿元,所募集的资金拟全部用于偿还发行人即将到期中期票据本金[23济南高新MTN004B]</t>
+          <t>本期债券的募集资金拟用于生产性支出,偿还到期债务、补充流动资金、项目建设运营及其他符合法律法规的用途。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,平安银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,英大证券有限责任公司,中信建投证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>济南高新控股集团有限公司2026年度第七期中期票据</t>
+          <t>龙源电力集团股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7661,25 +7647,29 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -7687,27 +7677,27 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7722,7 +7712,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7740,7 +7730,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26深能Y3</t>
+          <t>26远东五</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7750,64 +7740,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>524972.SZ</t>
+          <t>245933.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
         <v>1.75</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>49.72</v>
+        <v>51.68</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24深能Y2</t>
+          <t>24远东四</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>3.26Y+N</t>
+          <t>1.01Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7712</t>
+          <t>1.6727</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司</t>
+          <t>远东国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C 25.51</t>
+          <t>C- 21.30</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7831,17 +7821,17 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.68%~1.72%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7856,17 +7846,17 @@
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟用于偿还到期债务[23深能源MTN001]</t>
+          <t>本期公司债券募集资金拟用于偿还到期的银行借款和置换前期自有资金偿付的公司债券本金。[22远东七]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,国信证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7882,12 +7872,12 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>深圳能源集团股份有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)</t>
+          <t>远东国际融资租赁有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7897,12 +7887,12 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t>2028-08-26</t>
         </is>
       </c>
       <c r="AK33" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL33" s="3" t="inlineStr">
@@ -7922,37 +7912,37 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-08-26</t>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7962,12 +7952,12 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY33" s="3" t="inlineStr">
@@ -7980,7 +7970,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26龙源K1</t>
+          <t>26财融G4</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7990,7 +7980,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>524981.SZ</t>
+          <t>245953.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7999,55 +7989,55 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>37.72</v>
+        <v>57.72</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25龙源电力MTN001</t>
+          <t>24财通租赁MTN003</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>3.41Y</t>
+          <t>3.10Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7059</t>
+          <t>1.9054</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司</t>
+          <t>无锡财通融资租赁有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 24.41</t>
+          <t>C- 23.38</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8057,7 +8047,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-24 15:00</t>
+          <t>08-24 16:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8071,17 +8061,17 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.78</v>
+        <v>2.78</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8092,17 +8082,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟用于生产性支出,偿还到期债务、补充流动资金、项目建设运营及其他符合法律法规的用途。</t>
+          <t>本期债券募集资金不超过人民币5亿元(含人民币5亿元)，扣除发行费用后，拟全部用于置换前期偿还回售公司债券本金的自有资金[21财通02]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,英大证券有限责任公司,中信建投证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -8113,17 +8103,17 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>无锡财通融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8158,32 +8148,32 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8216,7 +8206,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26远东五</t>
+          <t>26中证K2</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8226,19 +8216,19 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>245933.SH</t>
+          <t>245960.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.0</v>
+        <v>60.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -8246,44 +8236,44 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>51.68</v>
+        <v>35.49</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24远东四</t>
+          <t>21中证11</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>1.01Y</t>
+          <t>4.87Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6727</t>
+          <t>1.6980</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 21.30</t>
+          <t>A- 63.91</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8307,17 +8297,17 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.72%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8332,28 +8322,28 @@
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期的银行借款和置换前期自有资金偿付的公司债券本金。[22远东七]</t>
+          <t>本期债券募集资金不低于70%的部分用于通过股权、债券、基金投资、做市服务等形式,专项支持科技创新领域业务,剩余部分用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,国信证券股份有限公司</t>
+          <t>招商证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8363,7 +8353,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
+          <t>中信证券股份有限公司2026年面向专业机构投资者公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8373,14 +8363,10 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8403,7 +8389,7 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -8413,22 +8399,22 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -8438,7 +8424,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8456,7 +8442,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26财融G4</t>
+          <t>26晋交01</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8466,49 +8452,49 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>245953.SH</t>
+          <t>283770.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>57.72</v>
+        <v>35.68</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24财通租赁MTN003</t>
+          <t>25晋交K1</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>3.10Y</t>
+          <t>1.79Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.9054</t>
+          <t>1.6767</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8518,12 +8504,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>无锡财通融资租赁有限公司</t>
+          <t>山西省交通开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 23.38</t>
+          <t>C- 23.75</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8533,7 +8519,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>08-24 16:00</t>
+          <t>08-24 14:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8547,17 +8533,17 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2.78</v>
+        <v>5.08</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8568,17 +8554,17 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>山西省</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过人民币5亿元(含人民币5亿元)，扣除发行费用后，拟全部用于置换前期偿还回售公司债券本金的自有资金[21财通02]</t>
+          <t>本期债券募集资金不超过人民币10亿元(含),拟全部用于偿还到期公司债务[25晋交投SCP001,25晋交投SCP002]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>首创证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8599,22 +8585,22 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>无锡财通融资租赁有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>山西省交通开发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t>2028-08-26</t>
         </is>
       </c>
       <c r="AK36" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL36" s="3" t="inlineStr">
@@ -8634,32 +8620,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6*无效</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8692,7 +8678,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26中证K2</t>
+          <t>26郑安02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8702,7 +8688,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>245960.SH</t>
+          <t>283741.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -8711,55 +8697,55 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>60.0</v>
+        <v>6.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>60.0</v>
+        <v>6.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>35.49</v>
+        <v>60.49</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>21中证11</t>
+          <t>26郑安01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.87Y</t>
+          <t>4.78Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6980</t>
+          <t>2.0141</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>2.0300/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>郑州城发安居科技有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>A- 63.91</t>
+          <t>B- 38.00</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8783,17 +8769,17 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8801,35 +8787,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不低于70%的部分用于通过股权、债券、基金投资、做市服务等形式,专项支持科技创新领域业务,剩余部分用于补充公司流动资金。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还合并范围内到期或回售的公司债券。[23郑住02]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>华泰联合证券有限责任公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8839,12 +8821,12 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司2026年面向专业机构投资者公开发行科技创新公司债券(第二期)</t>
+          <t>郑州城发安居科技有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
@@ -8870,32 +8852,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合地产</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>综合地产</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>计算机应用</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8928,7 +8910,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26晋交01</t>
+          <t>26嘉业03</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8938,64 +8920,64 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283770.SH</t>
+          <t>283663.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10.0</v>
+        <v>3.2</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.0</v>
+        <v>3.2</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>35.68</v>
+        <v>31.49</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25晋交K1</t>
+          <t>26嘉业K2</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1.79Y</t>
+          <t>2.90Y+2.00Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6767</t>
+          <t>1.7540</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7900/1.7400</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>山西省交通开发投资集团有限公司</t>
+          <t>上海嘉定工业区开发(集团)有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 23.75</t>
+          <t>B- 42.83</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9005,7 +8987,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>08-24 14:00</t>
+          <t>08-24 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -9019,38 +9001,38 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>5.08</v>
+        <v>3.75</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>山西省</t>
+          <t>上海市-嘉定区</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过人民币10亿元(含),拟全部用于偿还到期公司债务[25晋交投SCP001,25晋交投SCP002]</t>
+          <t>本期债券募集资金不超过3.20亿元(含3.20亿元),扣除发行费用后,拟全部用于偿还有息债务。[21嘉定工业MTN001]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>首创证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -9071,7 +9053,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>山西省交通开发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>上海嘉定工业区开发(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -9081,14 +9063,10 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9096,7 +9074,7 @@
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
@@ -9106,12 +9084,12 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6*无效</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -9121,22 +9099,22 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AV38" s="3" t="inlineStr">
@@ -9146,7 +9124,7 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
@@ -9164,7 +9142,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26郑安02</t>
+          <t>26青城11</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9174,30 +9152,30 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>283741.SH</t>
+          <t>283744.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+3+2</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>6.0</v>
+        <v>4.25</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6.0</v>
+        <v>8.5</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>60.49</v>
+        <v>29.06</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -9206,32 +9184,32 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26郑安01</t>
+          <t>26青城09</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.78Y</t>
+          <t>4.65Y+5.00Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.0141</t>
+          <t>1.9742</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>2.0300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>郑州城发安居科技有限公司</t>
+          <t>青岛城市建设投资(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 38.00</t>
+          <t>B- 38.99</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9241,7 +9219,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>08-24 15:00</t>
+          <t>08-24 16:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9254,18 +9232,16 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U39" s="4" t="n">
-        <v>2.17</v>
-      </c>
+      <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9276,17 +9252,17 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还合并范围内到期或回售的公司债券。[23郑住02]</t>
+          <t>本期债券募集资金拟全部用于偿还发行人到期的公司债券本金[23青城09]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,平安证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9307,7 +9283,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>郑州城发安居科技有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第六期)(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9317,7 +9293,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2036-08-26</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -9338,37 +9314,37 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>综合地产</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>综合地产</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>计算机应用</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AV39" s="3" t="inlineStr">
@@ -9378,7 +9354,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -9396,7 +9372,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26嘉业03</t>
+          <t>26桂资01</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9406,64 +9382,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>283663.SH</t>
+          <t>283760.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3.2</v>
+        <v>5.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3.2</v>
+        <v>5.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>31.49</v>
+        <v>93.72</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26嘉业K2</t>
+          <t>25桂金01</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.90Y+2.00Y</t>
+          <t>1.76Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.7540</t>
+          <t>2.1654</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.7900/1.7400</t>
+          <t>2.2000/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>上海嘉定工业区开发(集团)有限公司</t>
+          <t>广西资产管理有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 42.83</t>
+          <t>C+ 33.75</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9487,38 +9463,38 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>上海市-嘉定区</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过3.20亿元(含3.20亿元),扣除发行费用后,拟全部用于偿还有息债务。[21嘉定工业MTN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3.50亿元用于偿还到期债务,不超过1.50亿元用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>华创证券有限责任公司,国海证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9539,7 +9515,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>上海嘉定工业区开发(集团)有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>广西资产管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9549,10 +9525,14 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9560,7 +9540,7 @@
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
@@ -9570,37 +9550,37 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9610,7 +9590,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9628,59 +9608,59 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26青城11</t>
+          <t>26北新建材SCP008</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>08-24 19:00</t>
+          <t>08-24 18:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283744.SH</t>
+          <t>012682135.IB</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5+3+2</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4.25</v>
+        <v>6.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>8.5</v>
+        <v>6.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.36 ~ 1.54</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.97</v>
+        <v>1.41</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>29.06</v>
+        <v>25.42</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26青城09</t>
+          <t>26北新建材SCP006</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.65Y+5.00Y</t>
+          <t>214D</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.9742</t>
+          <t>1.5534</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9690,12 +9670,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>青岛城市建设投资(集团)有限责任公司</t>
+          <t>北新建材集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 38.99</t>
+          <t>C- 24.59</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9705,7 +9685,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>08-24 16:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9715,19 +9695,21 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="U41" s="3"/>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>1.9667</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9738,101 +9720,101 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还发行人到期的公司债券本金[23青城09]</t>
+          <t>本期超短期融资券发行拟募集资金6亿元，全部用于偿还本部及下属子公司有息债务和补充营运资金。</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,招商证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>青岛城市建设投资(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第六期)(品种一)</t>
+          <t>北新建材集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2036-08-26</t>
+          <t>2027-04-15</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9840,7 +9822,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9858,17 +9840,17 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26桂资01</t>
+          <t>26甘肃农垦MTN002(乡村振兴)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>08-24 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283760.SH</t>
+          <t>102683329.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9877,55 +9859,55 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>93.72</v>
+        <v>59.67</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25桂金01</t>
+          <t>26甘肃农垦MTN001(乡村振兴)</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1.76Y</t>
+          <t>2.45Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.1654</t>
+          <t>1.8753</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>2.2000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>广西资产管理有限公司</t>
+          <t>甘肃省农垦集团有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.75</t>
+          <t>C 29.17</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9935,7 +9917,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-24 15:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9949,9 +9931,11 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V42" s="3"/>
+        <v>3.3333</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
           <t>6-</t>
@@ -9959,34 +9943,42 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>甘肃省-兰州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3.50亿元用于偿还到期债务,不超过1.50亿元用于补充流动资金。</t>
+          <t>本期中期票据拟募集资金6亿元,其中:4.2亿元用于偿还发行人到期债务融资工具本金;1.8亿元用于乡村振兴领域。[23甘肃农垦MTN002(乡村振兴)]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>华创证券有限责任公司,国海证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3"/>
+          <t>招商银行股份有限公司,中国农业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>甘肃省国有资产投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9996,17 +9988,17 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>广西资产管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>甘肃省农垦集团有限责任公司2026年度第二期中期票据(乡村振兴)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
@@ -10021,57 +10013,57 @@
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>农业综合</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>资产管理</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
@@ -10086,7 +10078,7 @@
       </c>
       <c r="AY42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AZ42" s="3"/>
@@ -10094,74 +10086,74 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26德阳经开MTN001A</t>
+          <t>26安租Y6</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-24 18:00</t>
+          <t>08-24 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>102683295.IB</t>
+          <t>245894.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>4.0</v>
+        <v>4.5</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>66.49</v>
+        <v>88.72</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>25德阳经开MTN001</t>
+          <t>26安租Y4</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>3.52Y</t>
+          <t>1.64Y+N</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.2598</t>
+          <t>1.9643</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>2.2500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>德阳经开区发展(控股)集团有限公司</t>
+          <t>平安国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.10</t>
+          <t>C- 19.33</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10171,7 +10163,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>08-24 10:00</t>
+          <t>08-24 15:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10181,28 +10173,26 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>3.22</v>
+      </c>
+      <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -10212,42 +10202,38 @@
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>四川省-德阳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10.00亿元，拟使用募集资金10.00亿元偿还有息债务[21德阳经开MTN001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司到期或回售的公司债券本金或置换偿还公司债券本金的自有资金[21安租08,24安租Y2,22安租17]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,成都银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>双城(重庆)信用增进股份有限公司</t>
-        </is>
-      </c>
+          <t>平安证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种一)</t>
+          <t>平安国际融资租赁有限公司2026年面向专业投资者公开发行可续期公司债券(第三期)(品种二)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10257,53 +10243,57 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
-        </is>
-      </c>
-      <c r="AK43" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10313,17 +10303,17 @@
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY43" s="3" t="inlineStr">
@@ -10336,7 +10326,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26云投MTN006</t>
+          <t>26德阳经开MTN001A</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10346,64 +10336,64 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>102683298.IB</t>
+          <t>102683295.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.75 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>57.72</v>
+        <v>66.49</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>24云投MTN012</t>
+          <t>25德阳经开MTN001</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>3.00Y</t>
+          <t>3.52Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.9454</t>
+          <t>2.2598</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2500/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>云南省投资控股集团有限公司</t>
+          <t>德阳经开区发展(控股)集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.58</t>
+          <t>D+ 5.10</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10413,7 +10403,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-24 14:00</t>
+          <t>08-24 10:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10427,43 +10417,51 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>3.93</v>
+        <v>5.8</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>云南省</t>
+          <t>四川省-德阳市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为10.00亿元,募集资金扣除承销费后用于偿还发行人有息债务[24云投MTN020]</t>
+          <t>发行人本期中期票据发行金额为10.00亿元，拟使用募集资金10.00亿元偿还有息债务[21德阳经开MTN001]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD44" s="3"/>
+          <t>长江证券股份有限公司,成都银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>双城(重庆)信用增进股份有限公司</t>
+        </is>
+      </c>
       <c r="AE44" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -10481,7 +10479,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>云南省投资控股集团有限公司2026年度第六期中期票据</t>
+          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10491,14 +10489,10 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2029-08-25</t>
-        </is>
-      </c>
-      <c r="AK44" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-25</t>
+        </is>
+      </c>
+      <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -10516,32 +10510,32 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10551,7 +10545,7 @@
       </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW44" s="3" t="inlineStr">
@@ -10569,14 +10563,12 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ44" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ44" s="3"/>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26北新建材SCP008</t>
+          <t>26云投MTN006</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10586,49 +10578,49 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>012682135.IB</t>
+          <t>102683298.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.36 ~ 1.54</t>
+          <t>1.75 ~ 2.00</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>25.42</v>
+        <v>57.72</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26北新建材SCP006</t>
+          <t>24云投MTN012</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>214D</t>
+          <t>3.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.5534</t>
+          <t>1.9454</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10638,12 +10630,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>北新建材集团有限公司</t>
+          <t>云南省投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 24.59</t>
+          <t>C+ 32.58</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10653,7 +10645,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-24 09:00</t>
+          <t>08-24 14:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10667,17 +10659,19 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V45" s="3"/>
+        <v>3.93</v>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10688,28 +10682,28 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>云南省</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行拟募集资金6亿元，全部用于偿还本部及下属子公司有息债务和补充营运资金。</t>
+          <t>本期中期票据发行金额为10.00亿元,募集资金扣除承销费后用于偿还发行人有息债务[24云投MTN020]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10719,7 +10713,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>北新建材集团有限公司2026年度第八期超短期融资券</t>
+          <t>云南省投资控股集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10729,10 +10723,14 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2027-04-15</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2029-08-25</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
@@ -10740,7 +10738,7 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10755,27 +10753,27 @@
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10803,7 +10801,9 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">

--- a/data/credit_bond_all_2026-08-24.xlsx
+++ b/data/credit_bond_all_2026-08-24.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 43.63</t>
+          <t>B- 46.34</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>B- 42.50</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 23.10</t>
+          <t>C- 23.26</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 38.99</t>
+          <t>B- 40.34</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 19.33</t>
+          <t>C- 20.76</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2695,7 +2695,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 39.65</t>
+          <t>B- 38.75</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 45.38</t>
+          <t>B- 35.77</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 27.86</t>
+          <t>C 28.57</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 26.02</t>
+          <t>C 26.39</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 24.17</t>
+          <t>C 28.52</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.10</t>
+          <t>C- 19.75</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 45.38</t>
+          <t>B- 35.77</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.93</t>
+          <t>B- 36.54</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 41.86</t>
+          <t>B- 41.88</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B- 41.86</t>
+          <t>B- 41.88</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C 25.18</t>
+          <t>C 26.99</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C- 21.87</t>
+          <t>C- 22.97</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B- 35.78</t>
+          <t>B- 37.11</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 24.31</t>
+          <t>C 26.89</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>D- 1.43</t>
+          <t>D- 2.65</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 21.93</t>
+          <t>C- 21.26</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>C+ 34.64</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 23.10</t>
+          <t>C- 23.26</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C 25.51</t>
+          <t>C 25.62</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 24.41</t>
+          <t>C 25.96</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 21.30</t>
+          <t>C- 21.80</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 23.38</t>
+          <t>C- 22.93</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>A- 63.91</t>
+          <t>A- 65.02</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8369,7 +8369,7 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8837,7 +8837,7 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 42.83</t>
+          <t>B 50.59</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 38.99</t>
+          <t>B- 40.34</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9299,7 +9299,7 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 24.59</t>
+          <t>C- 20.96</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C 29.17</t>
+          <t>B- 39.72</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 19.33</t>
+          <t>C- 20.76</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.10</t>
+          <t>C- 19.75</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.58</t>
+          <t>C+ 34.03</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B- 45.40</t>
+          <t>B- 42.25</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.44</t>
+          <t>B- 38.15</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C 28.61</t>
+          <t>C+ 30.29</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B 51.09</t>
+          <t>B- 49.10</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.27</t>
+          <t>B- 35.42</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 37.05</t>
+          <t>C+ 33.94</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C 28.11</t>
+          <t>C+ 33.39</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>B- 45.60</t>
+          <t>B- 40.23</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>B- 41.97</t>
+          <t>B- 40.76</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.43</t>
+          <t>C+ 33.53</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.61</t>
+          <t>B- 36.03</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.00</t>
+          <t>C- 17.00</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.71</t>
+          <t>C 28.03</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.15</t>
+          <t>D+ 5.54</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.15</t>
+          <t>D+ 5.54</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>B- 38.74</t>
+          <t>B- 41.67</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>D- 2.50</t>
+          <t>D+ 6.50</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -16169,7 +16169,11 @@
           <t>产业控股</t>
         </is>
       </c>
-      <c r="AT68" s="3"/>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>元件</t>
+        </is>
+      </c>
       <c r="AU68" s="3" t="inlineStr">
         <is>
           <t/>
@@ -16267,7 +16271,7 @@
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>B- 38.74</t>
+          <t>B- 41.67</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16503,7 +16507,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C- 14.63</t>
+          <t>C- 15.75</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16741,7 +16745,7 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>B- 44.29</t>
+          <t>B- 44.97</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16977,7 +16981,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>B- 36.66</t>
+          <t>B- 37.05</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -17207,7 +17211,7 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 36.95</t>
+          <t>C+ 33.91</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17447,7 +17451,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C- 13.79</t>
+          <t>C- 15.61</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17683,7 +17687,7 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>C- 18.56</t>
+          <t>C- 16.09</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17917,7 +17921,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>B- 39.97</t>
+          <t>B- 42.14</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -18153,7 +18157,7 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.55</t>
+          <t>B- 35.01</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18385,7 +18389,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>B- 39.50</t>
+          <t>B- 40.83</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -19329,7 +19333,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C- 23.46</t>
+          <t>C- 23.85</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19567,7 +19571,7 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>B- 37.61</t>
+          <t>B- 38.41</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19663,7 +19667,7 @@
       </c>
       <c r="AL83" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM83" s="3" t="inlineStr">
@@ -19803,7 +19807,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>C- 11.04</t>
+          <t>C- 23.54</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -20041,7 +20045,7 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 11.62</t>
+          <t>C- 13.43</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -20133,7 +20137,7 @@
       <c r="AK85" s="3"/>
       <c r="AL85" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM85" s="3" t="inlineStr">
@@ -20737,7 +20741,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>B- 48.25</t>
+          <t>B+ 56.19</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -21073,7 +21077,7 @@
       <c r="AK89" s="3"/>
       <c r="AL89" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM89" s="3" t="inlineStr">
